--- a/Data_2021.xlsx
+++ b/Data_2021.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be89a93bd219aae1/Documentos/student_research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2881342A116A34CEEB3B98154B5DCE3A874E2485" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{044DD204-680E-4823-91E9-5E028355075F}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_2881342A116A34CEEB3B98154B5DCE3A874E2485" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DB7216D-A9F9-4AD3-AB73-E5FD0D4D95CF}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-2592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-2592" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="338">
   <si>
     <t>country</t>
   </si>
@@ -1053,8 +1054,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1082,8 +1091,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,6 +1121,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -40173,4 +40199,3814 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C01C5E-C38F-44D3-8350-2940E98516C7}">
+  <dimension ref="A1:Z48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="23" width="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="3">
+        <v>16.519186211923621</v>
+      </c>
+      <c r="E2" s="3">
+        <v>18.940781929046679</v>
+      </c>
+      <c r="F2" s="3">
+        <v>18.899185979899929</v>
+      </c>
+      <c r="G2" s="3">
+        <v>20.51439192809282</v>
+      </c>
+      <c r="H2" s="3">
+        <v>18.25257704695721</v>
+      </c>
+      <c r="I2" s="3">
+        <v>6.6388107931456481</v>
+      </c>
+      <c r="J2" s="3">
+        <v>19.315461479045801</v>
+      </c>
+      <c r="K2" s="3">
+        <v>25.021783478278088</v>
+      </c>
+      <c r="L2" s="3">
+        <v>20.51461974658919</v>
+      </c>
+      <c r="M2" s="3">
+        <v>48.366414144038643</v>
+      </c>
+      <c r="N2" s="3">
+        <v>42.558068145995001</v>
+      </c>
+      <c r="O2" s="3">
+        <v>64.548913409234629</v>
+      </c>
+      <c r="P2" s="3">
+        <v>63.152581219785731</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>58.819746012007244</v>
+      </c>
+      <c r="R2" s="3">
+        <v>66.894026424487762</v>
+      </c>
+      <c r="S2" s="3">
+        <v>76.232861171800664</v>
+      </c>
+      <c r="T2" s="3">
+        <v>80.377308700678739</v>
+      </c>
+      <c r="U2" s="3">
+        <v>76.648003898127428</v>
+      </c>
+      <c r="V2" s="3">
+        <v>4.3189064873642842</v>
+      </c>
+      <c r="W2" s="3">
+        <v>2.0506862399986452</v>
+      </c>
+      <c r="X2" s="3">
+        <v>1704</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>267</v>
+      </c>
+      <c r="Z2">
+        <v>8.8487812702276436</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.320779852619939</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10.262202124501631</v>
+      </c>
+      <c r="F3" s="3">
+        <v>10.81585433841893</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.613987125493439</v>
+      </c>
+      <c r="H3" s="3">
+        <v>6.777725581437549</v>
+      </c>
+      <c r="I3" s="3">
+        <v>3.5358432115866831</v>
+      </c>
+      <c r="J3" s="3">
+        <v>11.333177412958619</v>
+      </c>
+      <c r="K3" s="3">
+        <v>9.0582623296126119</v>
+      </c>
+      <c r="L3" s="3">
+        <v>12.40356889910144</v>
+      </c>
+      <c r="M3" s="3">
+        <v>50.879843152262339</v>
+      </c>
+      <c r="N3" s="3">
+        <v>48.237491848434964</v>
+      </c>
+      <c r="O3" s="3">
+        <v>34.506886570888042</v>
+      </c>
+      <c r="P3" s="3">
+        <v>33.495486794905887</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>59.814895352189488</v>
+      </c>
+      <c r="R3" s="3">
+        <v>32.511991487015692</v>
+      </c>
+      <c r="S3" s="3">
+        <v>71.85223691672023</v>
+      </c>
+      <c r="T3" s="3">
+        <v>69.793118226600726</v>
+      </c>
+      <c r="U3" s="3">
+        <v>61.219890526197631</v>
+      </c>
+      <c r="V3" s="3">
+        <v>2.9174197166216889</v>
+      </c>
+      <c r="W3" s="3">
+        <v>1.01259188866788</v>
+      </c>
+      <c r="X3" s="3">
+        <v>2010</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>167</v>
+      </c>
+      <c r="Z3">
+        <v>3.4221089419737978</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.2082924374995496</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10.02658605580409</v>
+      </c>
+      <c r="F4" s="3">
+        <v>11.40182377164736</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9.3548909794095323</v>
+      </c>
+      <c r="H4" s="3">
+        <v>6.1807895125674568</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5.1007831200532578</v>
+      </c>
+      <c r="J4" s="3">
+        <v>27.756736388547971</v>
+      </c>
+      <c r="K4" s="3">
+        <v>12.034724948911389</v>
+      </c>
+      <c r="L4" s="3">
+        <v>56.367299907921222</v>
+      </c>
+      <c r="M4" s="3">
+        <v>48.221845641574248</v>
+      </c>
+      <c r="N4" s="3">
+        <v>53.032626822994636</v>
+      </c>
+      <c r="O4" s="3">
+        <v>65.791912253512763</v>
+      </c>
+      <c r="P4" s="3">
+        <v>73.23920270434941</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>30.758168693545059</v>
+      </c>
+      <c r="R4" s="3">
+        <v>72.430253855727571</v>
+      </c>
+      <c r="S4" s="3">
+        <v>75.63421460897149</v>
+      </c>
+      <c r="T4" s="3">
+        <v>81.964038724860828</v>
+      </c>
+      <c r="U4" s="3">
+        <v>78.481858647102854</v>
+      </c>
+      <c r="V4" s="3">
+        <v>8.7195733839793572</v>
+      </c>
+      <c r="W4" s="3">
+        <v>2.1544778611206619</v>
+      </c>
+      <c r="X4" s="3">
+        <v>3123</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>295</v>
+      </c>
+      <c r="Z4">
+        <v>3.5597614155379902</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="3">
+        <v>17.490530005082039</v>
+      </c>
+      <c r="E5" s="3">
+        <v>19.333613772245041</v>
+      </c>
+      <c r="F5" s="3">
+        <v>19.04097099609346</v>
+      </c>
+      <c r="G5" s="3">
+        <v>14.848392888824259</v>
+      </c>
+      <c r="H5" s="3">
+        <v>16.744538329334819</v>
+      </c>
+      <c r="I5" s="3">
+        <v>15.117980769164721</v>
+      </c>
+      <c r="J5" s="3">
+        <v>33.561035966463578</v>
+      </c>
+      <c r="K5" s="3">
+        <v>25.150453164450312</v>
+      </c>
+      <c r="L5" s="3">
+        <v>29.714682637835519</v>
+      </c>
+      <c r="M5" s="3">
+        <v>49.321360708345303</v>
+      </c>
+      <c r="N5" s="3">
+        <v>53.032609332891347</v>
+      </c>
+      <c r="O5" s="3">
+        <v>69.693787257372179</v>
+      </c>
+      <c r="P5" s="3">
+        <v>57.875401560973991</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>37.600351037105902</v>
+      </c>
+      <c r="R5" s="3">
+        <v>67.601653386969517</v>
+      </c>
+      <c r="S5" s="3">
+        <v>81.821241857057814</v>
+      </c>
+      <c r="T5" s="3">
+        <v>81.924191690998995</v>
+      </c>
+      <c r="U5" s="3">
+        <v>83.517535260814881</v>
+      </c>
+      <c r="V5" s="3">
+        <v>10.48773514701225</v>
+      </c>
+      <c r="W5" s="3">
+        <v>3.413649954214617</v>
+      </c>
+      <c r="X5" s="3">
+        <v>3043</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>481</v>
+      </c>
+      <c r="Z5">
+        <v>5.1677376673414468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5.5298409244214</v>
+      </c>
+      <c r="E6" s="3">
+        <v>7.4998067758093399</v>
+      </c>
+      <c r="F6" s="3">
+        <v>6.2777243812880537</v>
+      </c>
+      <c r="G6" s="3">
+        <v>6.037064068966119</v>
+      </c>
+      <c r="H6" s="3">
+        <v>4.6280320562621418</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3.0089621149502159</v>
+      </c>
+      <c r="J6" s="3">
+        <v>7.406259366640815</v>
+      </c>
+      <c r="K6" s="3">
+        <v>17.742207699199621</v>
+      </c>
+      <c r="L6" s="3">
+        <v>10.946591311218061</v>
+      </c>
+      <c r="M6" s="3">
+        <v>55.846575056547742</v>
+      </c>
+      <c r="N6" s="3">
+        <v>51.459886837908257</v>
+      </c>
+      <c r="O6" s="3">
+        <v>53.09778407318386</v>
+      </c>
+      <c r="P6" s="3">
+        <v>48.634317694123787</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>32.566274233102718</v>
+      </c>
+      <c r="R6" s="3">
+        <v>35.123115844424923</v>
+      </c>
+      <c r="S6" s="3">
+        <v>64.792240498499737</v>
+      </c>
+      <c r="T6" s="3">
+        <v>64.109990447834264</v>
+      </c>
+      <c r="U6" s="3">
+        <v>56.54728286431461</v>
+      </c>
+      <c r="V6" s="3">
+        <v>1.6268479988504601</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0.38995935877408439</v>
+      </c>
+      <c r="X6" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>110</v>
+      </c>
+      <c r="Z6">
+        <v>14.68331133037446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D7" s="3">
+        <v>14.2108724303913</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13.807705267353009</v>
+      </c>
+      <c r="F7" s="3">
+        <v>16.81607400824107</v>
+      </c>
+      <c r="G7" s="3">
+        <v>19.565663230345191</v>
+      </c>
+      <c r="H7" s="3">
+        <v>13.79018421050201</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7.7358566120094814</v>
+      </c>
+      <c r="J7" s="3">
+        <v>14.973585048172881</v>
+      </c>
+      <c r="K7" s="3">
+        <v>19.99288288930288</v>
+      </c>
+      <c r="L7" s="3">
+        <v>22.481829721463988</v>
+      </c>
+      <c r="M7" s="3">
+        <v>35.361817703592401</v>
+      </c>
+      <c r="N7" s="3">
+        <v>36.828007892831209</v>
+      </c>
+      <c r="O7" s="3">
+        <v>45.413729753448337</v>
+      </c>
+      <c r="P7" s="3">
+        <v>69.927955929668371</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>56.751325794667153</v>
+      </c>
+      <c r="R7" s="3">
+        <v>85.641780774153801</v>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3">
+        <v>3.46382146778741</v>
+      </c>
+      <c r="W7" s="3">
+        <v>2.428528359090155</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1718</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>246</v>
+      </c>
+      <c r="Z7">
+        <v>6.3734128689538316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.700761724747986</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7.4787075293066332</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10.986323109136571</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10.45286130319618</v>
+      </c>
+      <c r="H8" s="3">
+        <v>6.9599566838812423</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2.898847209333542</v>
+      </c>
+      <c r="J8" s="3">
+        <v>14.10589509439472</v>
+      </c>
+      <c r="K8" s="3">
+        <v>8.0173452836826353</v>
+      </c>
+      <c r="L8" s="3">
+        <v>16.85367751100743</v>
+      </c>
+      <c r="M8" s="3">
+        <v>49.737648841070737</v>
+      </c>
+      <c r="N8" s="3">
+        <v>44.078890071013113</v>
+      </c>
+      <c r="O8" s="3">
+        <v>48.605020635620157</v>
+      </c>
+      <c r="P8" s="3">
+        <v>52.133649909149213</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>46.305045817608672</v>
+      </c>
+      <c r="R8" s="3">
+        <v>51.998969337177691</v>
+      </c>
+      <c r="S8" s="3">
+        <v>68.497745405743188</v>
+      </c>
+      <c r="T8" s="3">
+        <v>55.413941956938856</v>
+      </c>
+      <c r="U8" s="3">
+        <v>75.944440822192078</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1.635219401261891</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.91412436090380844</v>
+      </c>
+      <c r="X8" s="3">
+        <v>3791</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>287</v>
+      </c>
+      <c r="Z8">
+        <v>3.55812878059271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.5225169435739536</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.9265774366729769</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6.8250965602248748</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6.7554421409003877</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5.9719874188943907</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.773627789677374</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4.8908147048844466</v>
+      </c>
+      <c r="K9" s="3">
+        <v>11.757074823629489</v>
+      </c>
+      <c r="L9" s="3">
+        <v>8.9970138177349952</v>
+      </c>
+      <c r="M9" s="3">
+        <v>58.432414632392963</v>
+      </c>
+      <c r="N9" s="3">
+        <v>51.030768636696919</v>
+      </c>
+      <c r="O9" s="3">
+        <v>49.750407716033052</v>
+      </c>
+      <c r="P9" s="3">
+        <v>30.023274583432759</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>38.102049641809877</v>
+      </c>
+      <c r="R9" s="3">
+        <v>35.912174749799973</v>
+      </c>
+      <c r="S9" s="3">
+        <v>49.983041957649867</v>
+      </c>
+      <c r="T9" s="3">
+        <v>60.697707444401303</v>
+      </c>
+      <c r="U9" s="3">
+        <v>47.850304691787429</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1.524862830868452</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0.63958838981896038</v>
+      </c>
+      <c r="X9" s="3">
+        <v>31785</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>1589</v>
+      </c>
+      <c r="Z9">
+        <v>7.1685551509942798</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.7497940971915842</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9.1030525363089403</v>
+      </c>
+      <c r="F10" s="3">
+        <v>13.27069548865914</v>
+      </c>
+      <c r="G10" s="3">
+        <v>12.56405327371405</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9.6107464694023506</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.8833805288642309</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9.8400410833360379</v>
+      </c>
+      <c r="K10" s="3">
+        <v>15.74663413001497</v>
+      </c>
+      <c r="L10" s="3">
+        <v>10.65871204363931</v>
+      </c>
+      <c r="M10" s="3">
+        <v>38.209365134945713</v>
+      </c>
+      <c r="N10" s="3">
+        <v>33.719570052236669</v>
+      </c>
+      <c r="O10" s="3">
+        <v>35.997625670514118</v>
+      </c>
+      <c r="P10" s="3">
+        <v>36.542086174766943</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>49.739943333013457</v>
+      </c>
+      <c r="R10" s="3">
+        <v>49.073442847216903</v>
+      </c>
+      <c r="S10" s="3">
+        <v>64.202695236487699</v>
+      </c>
+      <c r="T10" s="3">
+        <v>64.454721611936264</v>
+      </c>
+      <c r="U10" s="3">
+        <v>65.459411712174926</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1.6924708266474719</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0.45538081046545459</v>
+      </c>
+      <c r="X10" s="3">
+        <v>2014</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>197</v>
+      </c>
+      <c r="Z10">
+        <v>8.3635950006205988</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4.8256593804461154</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.8884693096202461</v>
+      </c>
+      <c r="F11" s="3">
+        <v>11.09971604558126</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5.2714148756749566</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2.3268450218528449</v>
+      </c>
+      <c r="I11" s="3">
+        <v>2.815398414913088</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4.2479318389585536</v>
+      </c>
+      <c r="K11" s="3">
+        <v>9.7173984965082632</v>
+      </c>
+      <c r="L11" s="3">
+        <v>11.149464614651119</v>
+      </c>
+      <c r="M11" s="3">
+        <v>50.929453438987153</v>
+      </c>
+      <c r="N11" s="3">
+        <v>45.283916308641089</v>
+      </c>
+      <c r="O11" s="3">
+        <v>44.699295217256527</v>
+      </c>
+      <c r="P11" s="3">
+        <v>34.668793369972349</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>41.11630967621759</v>
+      </c>
+      <c r="R11" s="3">
+        <v>16.57293428027246</v>
+      </c>
+      <c r="S11" s="3">
+        <v>61.101690876670382</v>
+      </c>
+      <c r="T11" s="3">
+        <v>56.321035940545549</v>
+      </c>
+      <c r="U11" s="3">
+        <v>65.488025133285362</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.96707888234416151</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.36016478816856901</v>
+      </c>
+      <c r="X11" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>95</v>
+      </c>
+      <c r="Z11">
+        <v>4.4687408225392229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9.6846256242408373</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7.8540438506263621</v>
+      </c>
+      <c r="F12" s="3">
+        <v>13.156294189983591</v>
+      </c>
+      <c r="G12" s="3">
+        <v>13.57837492105557</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7.6332207147136417</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4.1185971970688584</v>
+      </c>
+      <c r="J12" s="3">
+        <v>14.99064374354368</v>
+      </c>
+      <c r="K12" s="3">
+        <v>14.5366106574042</v>
+      </c>
+      <c r="L12" s="3">
+        <v>14.93104992049874</v>
+      </c>
+      <c r="M12" s="3">
+        <v>55.642733348646331</v>
+      </c>
+      <c r="N12" s="3">
+        <v>48.248314599192213</v>
+      </c>
+      <c r="O12" s="3">
+        <v>50.020163357850357</v>
+      </c>
+      <c r="P12" s="3">
+        <v>49.12603634793988</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>37.664298793425161</v>
+      </c>
+      <c r="R12" s="3">
+        <v>27.039524703426881</v>
+      </c>
+      <c r="S12" s="3">
+        <v>67.783528659076353</v>
+      </c>
+      <c r="T12" s="3">
+        <v>72.251869396523276</v>
+      </c>
+      <c r="U12" s="3">
+        <v>68.077762890426456</v>
+      </c>
+      <c r="V12" s="3">
+        <v>1.825535241670005</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0.77341798649554239</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1618</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>158</v>
+      </c>
+      <c r="Z12">
+        <v>4.0988446231899296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9.7993147419702051</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8.1502771842329409</v>
+      </c>
+      <c r="F13" s="3">
+        <v>9.2435372969618737</v>
+      </c>
+      <c r="G13" s="3">
+        <v>11.75995744622494</v>
+      </c>
+      <c r="H13" s="3">
+        <v>11.652176872670861</v>
+      </c>
+      <c r="I13" s="3">
+        <v>7.1950604989323956</v>
+      </c>
+      <c r="J13" s="3">
+        <v>13.888862342130491</v>
+      </c>
+      <c r="K13" s="3">
+        <v>16.79209497390751</v>
+      </c>
+      <c r="L13" s="3">
+        <v>18.37997323956435</v>
+      </c>
+      <c r="M13" s="3">
+        <v>38.174702719965069</v>
+      </c>
+      <c r="N13" s="3">
+        <v>30.432656671383391</v>
+      </c>
+      <c r="O13" s="3">
+        <v>49.568087961171777</v>
+      </c>
+      <c r="P13" s="3">
+        <v>54.707645668252361</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>54.723574146773949</v>
+      </c>
+      <c r="R13" s="3">
+        <v>68.869345470079892</v>
+      </c>
+      <c r="S13" s="3">
+        <v>40.456734437266917</v>
+      </c>
+      <c r="T13" s="3">
+        <v>75.793636383680337</v>
+      </c>
+      <c r="U13" s="3">
+        <v>61.372461010994513</v>
+      </c>
+      <c r="V13" s="3">
+        <v>1.9209956123051191</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1.0093326864739349</v>
+      </c>
+      <c r="X13" s="3">
+        <v>1537</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>145</v>
+      </c>
+      <c r="Z13">
+        <v>7.1001363087863663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D14" s="3">
+        <v>12.575065625140841</v>
+      </c>
+      <c r="E14" s="3">
+        <v>16.974568796199112</v>
+      </c>
+      <c r="F14" s="3">
+        <v>15.423594870019061</v>
+      </c>
+      <c r="G14" s="3">
+        <v>16.001362545176971</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7.7698524906967688</v>
+      </c>
+      <c r="I14" s="3">
+        <v>8.1885516853896299</v>
+      </c>
+      <c r="J14" s="3">
+        <v>10.612266341529541</v>
+      </c>
+      <c r="K14" s="3">
+        <v>15.534461380229461</v>
+      </c>
+      <c r="L14" s="3">
+        <v>12.12983219989529</v>
+      </c>
+      <c r="M14" s="3">
+        <v>58.35811886848122</v>
+      </c>
+      <c r="N14" s="3">
+        <v>51.83527541079971</v>
+      </c>
+      <c r="O14" s="3">
+        <v>51.052237315722003</v>
+      </c>
+      <c r="P14" s="3">
+        <v>61.22154885651134</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>49.790647743884783</v>
+      </c>
+      <c r="R14" s="3">
+        <v>70.703745296549812</v>
+      </c>
+      <c r="S14" s="3">
+        <v>70.398082805095768</v>
+      </c>
+      <c r="T14" s="3">
+        <v>83.484973627561587</v>
+      </c>
+      <c r="U14" s="3">
+        <v>82.366068410704401</v>
+      </c>
+      <c r="V14" s="3">
+        <v>2.1002361068139259</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.61616087762833127</v>
+      </c>
+      <c r="X14" s="3">
+        <v>1598</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>201</v>
+      </c>
+      <c r="Z14">
+        <v>5.2885320505321447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.9660959317898374</v>
+      </c>
+      <c r="E15" s="3">
+        <v>9.7952746605816792</v>
+      </c>
+      <c r="F15" s="3">
+        <v>8.9234843095655147</v>
+      </c>
+      <c r="G15" s="3">
+        <v>11.17769731882176</v>
+      </c>
+      <c r="H15" s="3">
+        <v>8.1547992754509426</v>
+      </c>
+      <c r="I15" s="3">
+        <v>7.0025997895819776</v>
+      </c>
+      <c r="J15" s="3">
+        <v>8.2547677578981755</v>
+      </c>
+      <c r="K15" s="3">
+        <v>14.530467780046891</v>
+      </c>
+      <c r="L15" s="3">
+        <v>15.006376721967181</v>
+      </c>
+      <c r="M15" s="3">
+        <v>44.049724066043382</v>
+      </c>
+      <c r="N15" s="3">
+        <v>43.639640375876873</v>
+      </c>
+      <c r="O15" s="3">
+        <v>49.900506462798113</v>
+      </c>
+      <c r="P15" s="3">
+        <v>79.607310106623842</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>55.059165228916839</v>
+      </c>
+      <c r="R15" s="3">
+        <v>82.623652561829559</v>
+      </c>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3">
+        <v>2.6462723999517381</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0.94065093062949234</v>
+      </c>
+      <c r="X15" s="3">
+        <v>3746</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>326</v>
+      </c>
+      <c r="Z15">
+        <v>4.2921032563112842</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.087722057047674</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.8879961216164092</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.4954276302589931</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4.9013591946492552</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3.3932187895460029</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2.7311346668363208</v>
+      </c>
+      <c r="J16" s="3">
+        <v>2.840165267036006</v>
+      </c>
+      <c r="K16" s="3">
+        <v>6.211992007710947</v>
+      </c>
+      <c r="L16" s="3">
+        <v>5.6509290944887702</v>
+      </c>
+      <c r="M16" s="3">
+        <v>34.461992044781837</v>
+      </c>
+      <c r="N16" s="3">
+        <v>38.253909868463587</v>
+      </c>
+      <c r="O16" s="3">
+        <v>41.94684642231929</v>
+      </c>
+      <c r="P16" s="3">
+        <v>74.309735640818914</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>37.96951100354854</v>
+      </c>
+      <c r="R16" s="3">
+        <v>80.29779349234623</v>
+      </c>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3">
+        <v>0.54602965886762322</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.29508106805462941</v>
+      </c>
+      <c r="X16" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>61</v>
+      </c>
+      <c r="Z16">
+        <v>3.525033168613521</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" t="s">
+        <v>280</v>
+      </c>
+      <c r="C17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.9999747482670309</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.44459015077259528</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.295532646048005</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2.417614135785549</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1.6631866277495759</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.24076724655535681</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1.5738205034319921</v>
+      </c>
+      <c r="K17" s="3">
+        <v>13.25717227344683</v>
+      </c>
+      <c r="L17" s="3">
+        <v>3.6903357630384299</v>
+      </c>
+      <c r="M17" s="3">
+        <v>44.652389270212133</v>
+      </c>
+      <c r="N17" s="3">
+        <v>43.47525897031165</v>
+      </c>
+      <c r="O17" s="3">
+        <v>60.132381300961413</v>
+      </c>
+      <c r="P17" s="3">
+        <v>72.539243622023889</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>53.954061780619341</v>
+      </c>
+      <c r="R17" s="3">
+        <v>64.269242839064731</v>
+      </c>
+      <c r="S17" s="3">
+        <v>54.704949756743069</v>
+      </c>
+      <c r="T17" s="3">
+        <v>66.353695338633329</v>
+      </c>
+      <c r="U17" s="3">
+        <v>38.054464835808723</v>
+      </c>
+      <c r="V17" s="3">
+        <v>2.7975177578543722</v>
+      </c>
+      <c r="W17" s="3">
+        <v>1.677615126337987</v>
+      </c>
+      <c r="X17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>160</v>
+      </c>
+      <c r="Z17">
+        <v>11.05818386786755</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.9082153768966386</v>
+      </c>
+      <c r="E18" s="3">
+        <v>8.3251868784748222</v>
+      </c>
+      <c r="F18" s="3">
+        <v>10.03933010133064</v>
+      </c>
+      <c r="G18" s="3">
+        <v>9.5458295441298446</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5.1932084363423927</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.029570369556521</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8.2062940776035873</v>
+      </c>
+      <c r="K18" s="3">
+        <v>11.696696213631339</v>
+      </c>
+      <c r="L18" s="3">
+        <v>8.6442554058126984</v>
+      </c>
+      <c r="M18" s="3">
+        <v>45.498607309762463</v>
+      </c>
+      <c r="N18" s="3">
+        <v>37.926324198340453</v>
+      </c>
+      <c r="O18" s="3">
+        <v>37.133922628651931</v>
+      </c>
+      <c r="P18" s="3">
+        <v>48.172158250706239</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>39.881694740109921</v>
+      </c>
+      <c r="R18" s="3">
+        <v>38.232594360869712</v>
+      </c>
+      <c r="S18" s="3">
+        <v>50.637595820409118</v>
+      </c>
+      <c r="T18" s="3">
+        <v>82.649853608621214</v>
+      </c>
+      <c r="U18" s="3">
+        <v>57.931490604483038</v>
+      </c>
+      <c r="V18" s="3">
+        <v>2.1405814886152621</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1.111824410131123</v>
+      </c>
+      <c r="X18" s="3">
+        <v>3796</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>255</v>
+      </c>
+      <c r="Z18">
+        <v>4.9464904901786548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" s="3">
+        <v>20.978559484317131</v>
+      </c>
+      <c r="E19" s="3">
+        <v>15.650235940671349</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27.9202556687849</v>
+      </c>
+      <c r="G19" s="3">
+        <v>25.587968911015761</v>
+      </c>
+      <c r="H19" s="3">
+        <v>19.761719846374991</v>
+      </c>
+      <c r="I19" s="3">
+        <v>9.9902988390637386</v>
+      </c>
+      <c r="J19" s="3">
+        <v>22.295599549546001</v>
+      </c>
+      <c r="K19" s="3">
+        <v>27.783360864049602</v>
+      </c>
+      <c r="L19" s="3">
+        <v>50.04774381709732</v>
+      </c>
+      <c r="M19" s="3">
+        <v>48.409550971135843</v>
+      </c>
+      <c r="N19" s="3">
+        <v>45.05547510844881</v>
+      </c>
+      <c r="O19" s="3">
+        <v>66.723414706190127</v>
+      </c>
+      <c r="P19" s="3">
+        <v>54.80381530514569</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>70.628872471935068</v>
+      </c>
+      <c r="R19" s="3">
+        <v>42.010995926440671</v>
+      </c>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3">
+        <v>9.1342637465019418</v>
+      </c>
+      <c r="W19" s="3">
+        <v>2.170698464732784</v>
+      </c>
+      <c r="X19" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>419</v>
+      </c>
+      <c r="Z19">
+        <v>9.9482359515627952</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="3">
+        <v>29.885958550218259</v>
+      </c>
+      <c r="E20" s="3">
+        <v>24.70705110704381</v>
+      </c>
+      <c r="F20" s="3">
+        <v>38.544659664138422</v>
+      </c>
+      <c r="G20" s="3">
+        <v>33.937711558411067</v>
+      </c>
+      <c r="H20" s="3">
+        <v>28.460333873174509</v>
+      </c>
+      <c r="I20" s="3">
+        <v>18.95874561061693</v>
+      </c>
+      <c r="J20" s="3">
+        <v>32.224010641030397</v>
+      </c>
+      <c r="K20" s="3">
+        <v>26.562341410950971</v>
+      </c>
+      <c r="L20" s="3">
+        <v>51.445540060403758</v>
+      </c>
+      <c r="M20" s="3">
+        <v>49.720552395274588</v>
+      </c>
+      <c r="N20" s="3">
+        <v>46.783451566108177</v>
+      </c>
+      <c r="O20" s="3">
+        <v>70.722215023072565</v>
+      </c>
+      <c r="P20" s="3">
+        <v>59.748497035412413</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>70.720469475008215</v>
+      </c>
+      <c r="R20" s="3">
+        <v>48.038015999263372</v>
+      </c>
+      <c r="S20" s="3">
+        <v>78.829377863475585</v>
+      </c>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3">
+        <v>6.8840091346870356</v>
+      </c>
+      <c r="W20" s="3">
+        <v>2.1178201385004711</v>
+      </c>
+      <c r="X20" s="3">
+        <v>8540</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>2476</v>
+      </c>
+      <c r="Z20">
+        <v>7.1272866568944213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="3">
+        <v>15.687076566436501</v>
+      </c>
+      <c r="E21" s="3">
+        <v>15.06617836557016</v>
+      </c>
+      <c r="F21" s="3">
+        <v>18.035396679570109</v>
+      </c>
+      <c r="G21" s="3">
+        <v>18.448485332103459</v>
+      </c>
+      <c r="H21" s="3">
+        <v>14.24735442610681</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10.202456496513159</v>
+      </c>
+      <c r="J21" s="3">
+        <v>22.78653535682318</v>
+      </c>
+      <c r="K21" s="3">
+        <v>13.433016567140241</v>
+      </c>
+      <c r="L21" s="3">
+        <v>25.740477797444751</v>
+      </c>
+      <c r="M21" s="3">
+        <v>47.625146019632929</v>
+      </c>
+      <c r="N21" s="3">
+        <v>48.69977235383093</v>
+      </c>
+      <c r="O21" s="3">
+        <v>56.236937699335108</v>
+      </c>
+      <c r="P21" s="3">
+        <v>38.105472268672472</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>58.182983273209693</v>
+      </c>
+      <c r="R21" s="3">
+        <v>28.96265804895511</v>
+      </c>
+      <c r="S21" s="3">
+        <v>52.212356776410047</v>
+      </c>
+      <c r="T21" s="3">
+        <v>61.90469682101174</v>
+      </c>
+      <c r="U21" s="3">
+        <v>58.998940328026713</v>
+      </c>
+      <c r="V21" s="3">
+        <v>5.403245616269972</v>
+      </c>
+      <c r="W21" s="3">
+        <v>1.210273221713283</v>
+      </c>
+      <c r="X21" s="3">
+        <v>2052</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>326</v>
+      </c>
+      <c r="Z21">
+        <v>1.830537963846707</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="3">
+        <v>6.2703243972081131</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4.4466650012490536</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7.1624803767660827</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7.4119155780642503</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5.5982122392848694</v>
+      </c>
+      <c r="I22" s="3">
+        <v>6.1476817401259387</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9.9936548223350083</v>
+      </c>
+      <c r="K22" s="3">
+        <v>10.72483740482231</v>
+      </c>
+      <c r="L22" s="3">
+        <v>6.8353806808653301</v>
+      </c>
+      <c r="M22" s="3">
+        <v>39.533431154822047</v>
+      </c>
+      <c r="N22" s="3">
+        <v>47.856758534106532</v>
+      </c>
+      <c r="O22" s="3">
+        <v>12.25673435177085</v>
+      </c>
+      <c r="P22" s="3">
+        <v>11.744756742334379</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>20.04515016233762</v>
+      </c>
+      <c r="R22" s="3">
+        <v>29.708898655965399</v>
+      </c>
+      <c r="S22" s="3">
+        <v>23.99304320328876</v>
+      </c>
+      <c r="T22" s="3">
+        <v>62.363261719341708</v>
+      </c>
+      <c r="U22" s="3">
+        <v>55.091286336843872</v>
+      </c>
+      <c r="V22" s="3">
+        <v>1.0296094204497559</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0.57057027284263839</v>
+      </c>
+      <c r="X22" s="3">
+        <v>2013</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>133</v>
+      </c>
+      <c r="Z22">
+        <v>4.803002062182733</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D23" s="3">
+        <v>13.38935064938077</v>
+      </c>
+      <c r="E23" s="3">
+        <v>8.2644628099515263</v>
+      </c>
+      <c r="F23" s="3">
+        <v>12.533333333333269</v>
+      </c>
+      <c r="G23" s="3">
+        <v>14.584717607940791</v>
+      </c>
+      <c r="H23" s="3">
+        <v>13.93939393939381</v>
+      </c>
+      <c r="I23" s="3">
+        <v>15.08138150076587</v>
+      </c>
+      <c r="J23" s="3">
+        <v>18.839350649413781</v>
+      </c>
+      <c r="K23" s="3">
+        <v>23.525194805192161</v>
+      </c>
+      <c r="L23" s="3">
+        <v>35.19635516617533</v>
+      </c>
+      <c r="M23" s="3">
+        <v>21.735941558431321</v>
+      </c>
+      <c r="N23" s="3">
+        <v>14.716896768647411</v>
+      </c>
+      <c r="O23" s="3">
+        <v>53.950248959479971</v>
+      </c>
+      <c r="P23" s="3">
+        <v>43.994014029387458</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>40.46187709962539</v>
+      </c>
+      <c r="R23" s="3">
+        <v>34.957666303186322</v>
+      </c>
+      <c r="S23" s="3">
+        <v>57.127104228384027</v>
+      </c>
+      <c r="T23" s="3">
+        <v>89.382757106802472</v>
+      </c>
+      <c r="U23" s="3">
+        <v>71.35888194660096</v>
+      </c>
+      <c r="V23" s="3">
+        <v>2.5536363636154111</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1.1509090909069439</v>
+      </c>
+      <c r="X23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>268</v>
+      </c>
+      <c r="Z23">
+        <v>16.380519480498879</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" t="s">
+        <v>308</v>
+      </c>
+      <c r="C24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="3">
+        <v>15.69395377060431</v>
+      </c>
+      <c r="E24" s="3">
+        <v>15.510268427780121</v>
+      </c>
+      <c r="F24" s="3">
+        <v>16.995585232135451</v>
+      </c>
+      <c r="G24" s="3">
+        <v>17.28730106422168</v>
+      </c>
+      <c r="H24" s="3">
+        <v>16.205762209449428</v>
+      </c>
+      <c r="I24" s="3">
+        <v>9.9615053781227463</v>
+      </c>
+      <c r="J24" s="3">
+        <v>26.144736702526149</v>
+      </c>
+      <c r="K24" s="3">
+        <v>25.86008907821051</v>
+      </c>
+      <c r="L24" s="3">
+        <v>36.539920551415349</v>
+      </c>
+      <c r="M24" s="3">
+        <v>35.889744963922688</v>
+      </c>
+      <c r="N24" s="3">
+        <v>39.840176211152652</v>
+      </c>
+      <c r="O24" s="3">
+        <v>59.266002999175903</v>
+      </c>
+      <c r="P24" s="3">
+        <v>31.90000351593573</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>42.786212607140499</v>
+      </c>
+      <c r="R24" s="3">
+        <v>25.14261708530422</v>
+      </c>
+      <c r="S24" s="3">
+        <v>66.800178237253476</v>
+      </c>
+      <c r="T24" s="3">
+        <v>75.060330084319503</v>
+      </c>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3">
+        <v>6.321137054272052</v>
+      </c>
+      <c r="W24" s="3">
+        <v>1.704881802204862</v>
+      </c>
+      <c r="X24" s="3">
+        <v>2404</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>379</v>
+      </c>
+      <c r="Z24">
+        <v>11.005158189735649</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="3">
+        <v>14.36571354725965</v>
+      </c>
+      <c r="E25" s="3">
+        <v>12.76503678061443</v>
+      </c>
+      <c r="F25" s="3">
+        <v>15.435908740218039</v>
+      </c>
+      <c r="G25" s="3">
+        <v>14.648552864737191</v>
+      </c>
+      <c r="H25" s="3">
+        <v>17.885845817727809</v>
+      </c>
+      <c r="I25" s="3">
+        <v>9.4388327721660961</v>
+      </c>
+      <c r="J25" s="3">
+        <v>25.534841216850602</v>
+      </c>
+      <c r="K25" s="3">
+        <v>23.233324000086391</v>
+      </c>
+      <c r="L25" s="3">
+        <v>27.211248511264039</v>
+      </c>
+      <c r="M25" s="3">
+        <v>48.222324101623762</v>
+      </c>
+      <c r="N25" s="3">
+        <v>54.14104804435572</v>
+      </c>
+      <c r="O25" s="3">
+        <v>85.986828002690558</v>
+      </c>
+      <c r="P25" s="3">
+        <v>83.414913297294035</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>63.121257332052693</v>
+      </c>
+      <c r="R25" s="3">
+        <v>82.225770276177727</v>
+      </c>
+      <c r="S25" s="3">
+        <v>89.469306337417237</v>
+      </c>
+      <c r="T25" s="3">
+        <v>87.008518316478501</v>
+      </c>
+      <c r="U25" s="3">
+        <v>84.315424962665276</v>
+      </c>
+      <c r="V25" s="3">
+        <v>3.667685381800569</v>
+      </c>
+      <c r="W25" s="3">
+        <v>4.2427300671071002</v>
+      </c>
+      <c r="X25" s="3">
+        <v>3252</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>520</v>
+      </c>
+      <c r="Z25">
+        <v>8.5131521862875736</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8.7632368529326179</v>
+      </c>
+      <c r="E26" s="3">
+        <v>9.5200688466902967</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8.9776422472794231</v>
+      </c>
+      <c r="G26" s="3">
+        <v>14.714798210164311</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2.1389722196169001</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4.3049172178389323</v>
+      </c>
+      <c r="J26" s="3">
+        <v>27.456279135064321</v>
+      </c>
+      <c r="K26" s="3">
+        <v>15.52098156298087</v>
+      </c>
+      <c r="L26" s="3">
+        <v>27.551544877103801</v>
+      </c>
+      <c r="M26" s="3">
+        <v>39.923028688219077</v>
+      </c>
+      <c r="N26" s="3">
+        <v>20.22679560877777</v>
+      </c>
+      <c r="O26" s="3">
+        <v>66.436658135001764</v>
+      </c>
+      <c r="P26" s="3">
+        <v>17.866988133806281</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>41.871793622510893</v>
+      </c>
+      <c r="R26" s="3">
+        <v>17.72530505529544</v>
+      </c>
+      <c r="S26" s="3">
+        <v>54.306074497013491</v>
+      </c>
+      <c r="T26" s="3">
+        <v>88.71549933939059</v>
+      </c>
+      <c r="U26" s="3">
+        <v>50.656668348210829</v>
+      </c>
+      <c r="V26" s="3">
+        <v>4.6136717120642841</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.163663093541033</v>
+      </c>
+      <c r="X26" s="3">
+        <v>3136</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>292</v>
+      </c>
+      <c r="Z26">
+        <v>8.7940574932380287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="3">
+        <v>20.082966149673801</v>
+      </c>
+      <c r="E27" s="3">
+        <v>30.828454848119279</v>
+      </c>
+      <c r="F27" s="3">
+        <v>31.612655531793269</v>
+      </c>
+      <c r="G27" s="3">
+        <v>22.6221798145218</v>
+      </c>
+      <c r="H27" s="3">
+        <v>11.63796386329302</v>
+      </c>
+      <c r="I27" s="3">
+        <v>8.983085548053575</v>
+      </c>
+      <c r="J27" s="3">
+        <v>28.802780744734079</v>
+      </c>
+      <c r="K27" s="3">
+        <v>28.30686462176509</v>
+      </c>
+      <c r="L27" s="3">
+        <v>22.482471826629808</v>
+      </c>
+      <c r="M27" s="3">
+        <v>52.996602444187147</v>
+      </c>
+      <c r="N27" s="3">
+        <v>53.837765938620898</v>
+      </c>
+      <c r="O27" s="3">
+        <v>58.928482889337197</v>
+      </c>
+      <c r="P27" s="3">
+        <v>70.499761169454388</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>51.702710181685298</v>
+      </c>
+      <c r="R27" s="3">
+        <v>66.824749751760393</v>
+      </c>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3">
+        <v>5.640614299913647</v>
+      </c>
+      <c r="W27" s="3">
+        <v>5.9268861468597098</v>
+      </c>
+      <c r="X27" s="3">
+        <v>1658</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>323</v>
+      </c>
+      <c r="Z27">
+        <v>8.1502054433916307</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B28" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="3">
+        <v>6.092835824199792</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5.1562379562393996</v>
+      </c>
+      <c r="F28" s="3">
+        <v>7.4242018966869896</v>
+      </c>
+      <c r="G28" s="3">
+        <v>8.1577186940743367</v>
+      </c>
+      <c r="H28" s="3">
+        <v>5.0598215396483717</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.3844161027734758</v>
+      </c>
+      <c r="J28" s="3">
+        <v>15.03894718171224</v>
+      </c>
+      <c r="K28" s="3">
+        <v>10.817710716525809</v>
+      </c>
+      <c r="L28" s="3">
+        <v>41.577731489796413</v>
+      </c>
+      <c r="M28" s="3">
+        <v>37.948062085389942</v>
+      </c>
+      <c r="N28" s="3">
+        <v>35.470900304944102</v>
+      </c>
+      <c r="O28" s="3">
+        <v>61.476355974903903</v>
+      </c>
+      <c r="P28" s="3">
+        <v>64.126708038178066</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>43.970350618769132</v>
+      </c>
+      <c r="R28" s="3">
+        <v>56.047671284111701</v>
+      </c>
+      <c r="S28" s="3">
+        <v>85.135826338266639</v>
+      </c>
+      <c r="T28" s="3">
+        <v>79.721420919088942</v>
+      </c>
+      <c r="U28" s="3">
+        <v>80.61640612950869</v>
+      </c>
+      <c r="V28" s="3">
+        <v>4.2214446294812404</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0.35332393947089669</v>
+      </c>
+      <c r="X28" s="3">
+        <v>3064</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>186</v>
+      </c>
+      <c r="Z28">
+        <v>4.9110392751515208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B29" t="s">
+        <v>286</v>
+      </c>
+      <c r="C29" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="3">
+        <v>33.583150968319117</v>
+      </c>
+      <c r="E29" s="3">
+        <v>31.886290695137479</v>
+      </c>
+      <c r="F29" s="3">
+        <v>35.179741400699093</v>
+      </c>
+      <c r="G29" s="3">
+        <v>36.684233240487963</v>
+      </c>
+      <c r="H29" s="3">
+        <v>35.171689891233292</v>
+      </c>
+      <c r="I29" s="3">
+        <v>21.308120665433119</v>
+      </c>
+      <c r="J29" s="3">
+        <v>54.027185779563489</v>
+      </c>
+      <c r="K29" s="3">
+        <v>34.313986464860321</v>
+      </c>
+      <c r="L29" s="3">
+        <v>50.844809250391947</v>
+      </c>
+      <c r="M29" s="3">
+        <v>41.449351542737119</v>
+      </c>
+      <c r="N29" s="3">
+        <v>40.486909379021853</v>
+      </c>
+      <c r="O29" s="3">
+        <v>88.122372936754729</v>
+      </c>
+      <c r="P29" s="3">
+        <v>72.125067323654875</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>66.818571802699424</v>
+      </c>
+      <c r="R29" s="3">
+        <v>66.71464874636581</v>
+      </c>
+      <c r="S29" s="3">
+        <v>89.390272934780313</v>
+      </c>
+      <c r="T29" s="3">
+        <v>95.390564106429778</v>
+      </c>
+      <c r="U29" s="3">
+        <v>83.468746476719673</v>
+      </c>
+      <c r="V29" s="3">
+        <v>5.4285522146640908</v>
+      </c>
+      <c r="W29" s="3">
+        <v>7.6751516263957011</v>
+      </c>
+      <c r="X29" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>672</v>
+      </c>
+      <c r="Z29">
+        <v>8.1441229911444069</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B30" t="s">
+        <v>280</v>
+      </c>
+      <c r="C30" t="s">
+        <v>281</v>
+      </c>
+      <c r="D30" s="3">
+        <v>7.250558369498278</v>
+      </c>
+      <c r="E30" s="3">
+        <v>10.54369723404619</v>
+      </c>
+      <c r="F30" s="3">
+        <v>9.1929089387709624</v>
+      </c>
+      <c r="G30" s="3">
+        <v>8.6613916624243625</v>
+      </c>
+      <c r="H30" s="3">
+        <v>6.5910953982183358</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1.7112082263631849</v>
+      </c>
+      <c r="J30" s="3">
+        <v>11.33654457024755</v>
+      </c>
+      <c r="K30" s="3">
+        <v>8.5131973996528121</v>
+      </c>
+      <c r="L30" s="3">
+        <v>17.702404497509619</v>
+      </c>
+      <c r="M30" s="3">
+        <v>48.606548268239159</v>
+      </c>
+      <c r="N30" s="3">
+        <v>43.035418344490488</v>
+      </c>
+      <c r="O30" s="3">
+        <v>52.910920914404201</v>
+      </c>
+      <c r="P30" s="3">
+        <v>54.070459669567597</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>42.989985599908671</v>
+      </c>
+      <c r="R30" s="3">
+        <v>64.120378321901569</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3">
+        <v>2.274304952939151</v>
+      </c>
+      <c r="W30" s="3">
+        <v>1.8604025340469279</v>
+      </c>
+      <c r="X30" s="3">
+        <v>1991</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>156</v>
+      </c>
+      <c r="Z30">
+        <v>3.5824742618351069</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C31" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" s="3">
+        <v>12.497369865470819</v>
+      </c>
+      <c r="E31" s="3">
+        <v>16.35116749831208</v>
+      </c>
+      <c r="F31" s="3">
+        <v>16.933108153647559</v>
+      </c>
+      <c r="G31" s="3">
+        <v>12.41828933308032</v>
+      </c>
+      <c r="H31" s="3">
+        <v>9.8190030473349879</v>
+      </c>
+      <c r="I31" s="3">
+        <v>7.4344689895984102</v>
+      </c>
+      <c r="J31" s="3">
+        <v>16.11780242650719</v>
+      </c>
+      <c r="K31" s="3">
+        <v>19.262311674140509</v>
+      </c>
+      <c r="L31" s="3">
+        <v>20.084630693439181</v>
+      </c>
+      <c r="M31" s="3">
+        <v>53.701725047334307</v>
+      </c>
+      <c r="N31" s="3">
+        <v>49.860663574293987</v>
+      </c>
+      <c r="O31" s="3">
+        <v>57.78227196823569</v>
+      </c>
+      <c r="P31" s="3">
+        <v>57.292884629552141</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>57.54383785891708</v>
+      </c>
+      <c r="R31" s="3">
+        <v>58.869467333363168</v>
+      </c>
+      <c r="S31" s="3">
+        <v>67.022783745655303</v>
+      </c>
+      <c r="T31" s="3">
+        <v>83.034322747313325</v>
+      </c>
+      <c r="U31" s="3">
+        <v>82.557091868950621</v>
+      </c>
+      <c r="V31" s="3">
+        <v>4.3496993341921719</v>
+      </c>
+      <c r="W31" s="3">
+        <v>2.6351996562032838</v>
+      </c>
+      <c r="X31" s="3">
+        <v>2007</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>251</v>
+      </c>
+      <c r="Z31">
+        <v>6.9372614150473213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C32" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.368542346840858</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3.736065079843323</v>
+      </c>
+      <c r="F32" s="3">
+        <v>10.869971936389129</v>
+      </c>
+      <c r="G32" s="3">
+        <v>11.600090273076029</v>
+      </c>
+      <c r="H32" s="3">
+        <v>8.5360149672591241</v>
+      </c>
+      <c r="I32" s="3">
+        <v>4.5993636100665318</v>
+      </c>
+      <c r="J32" s="3">
+        <v>9.0791242558095604</v>
+      </c>
+      <c r="K32" s="3">
+        <v>11.50854618782418</v>
+      </c>
+      <c r="L32" s="3">
+        <v>17.297960435516181</v>
+      </c>
+      <c r="M32" s="3">
+        <v>53.101594008066343</v>
+      </c>
+      <c r="N32" s="3">
+        <v>50.075949367088832</v>
+      </c>
+      <c r="O32" s="3">
+        <v>64.047675521821816</v>
+      </c>
+      <c r="P32" s="3">
+        <v>50.174658621784857</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>72.912983696719934</v>
+      </c>
+      <c r="R32" s="3">
+        <v>50.849362152158292</v>
+      </c>
+      <c r="S32" s="3">
+        <v>81.89622281571944</v>
+      </c>
+      <c r="T32" s="3">
+        <v>75.396168777445538</v>
+      </c>
+      <c r="U32" s="3">
+        <v>66.575222894195534</v>
+      </c>
+      <c r="V32" s="3">
+        <v>3.4036363636363931</v>
+      </c>
+      <c r="W32" s="3">
+        <v>2.227770309199173</v>
+      </c>
+      <c r="X32" s="3">
+        <v>2092</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>186</v>
+      </c>
+      <c r="Z32">
+        <v>8.5990013443442255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C33" t="s">
+        <v>281</v>
+      </c>
+      <c r="D33" s="3">
+        <v>7.8887266494189996</v>
+      </c>
+      <c r="E33" s="3">
+        <v>6.466745273246385</v>
+      </c>
+      <c r="F33" s="3">
+        <v>9.5755190371380881</v>
+      </c>
+      <c r="G33" s="3">
+        <v>9.096043395901626</v>
+      </c>
+      <c r="H33" s="3">
+        <v>8.2014937383532818</v>
+      </c>
+      <c r="I33" s="3">
+        <v>5.6042699411477486</v>
+      </c>
+      <c r="J33" s="3">
+        <v>6.9529022157242384</v>
+      </c>
+      <c r="K33" s="3">
+        <v>17.51450913194207</v>
+      </c>
+      <c r="L33" s="3">
+        <v>11.83353069066696</v>
+      </c>
+      <c r="M33" s="3">
+        <v>48.82365966003762</v>
+      </c>
+      <c r="N33" s="3">
+        <v>44.525155779268928</v>
+      </c>
+      <c r="O33" s="3">
+        <v>42.75196350297896</v>
+      </c>
+      <c r="P33" s="3">
+        <v>61.041227394977547</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>64.138666589239151</v>
+      </c>
+      <c r="R33" s="3">
+        <v>69.567196674770315</v>
+      </c>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3">
+        <v>1.443827904778938</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0.47179667637821882</v>
+      </c>
+      <c r="X33" s="3">
+        <v>1983</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>149</v>
+      </c>
+      <c r="Z33">
+        <v>8.8792985886080231</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" t="s">
+        <v>280</v>
+      </c>
+      <c r="C34" t="s">
+        <v>281</v>
+      </c>
+      <c r="D34" s="3">
+        <v>15.133421141867251</v>
+      </c>
+      <c r="E34" s="3">
+        <v>25.655914649330249</v>
+      </c>
+      <c r="F34" s="3">
+        <v>20.30615999796975</v>
+      </c>
+      <c r="G34" s="3">
+        <v>21.820443932642011</v>
+      </c>
+      <c r="H34" s="3">
+        <v>9.72680399961639</v>
+      </c>
+      <c r="I34" s="3">
+        <v>4.0134035461321718</v>
+      </c>
+      <c r="J34" s="3">
+        <v>15.555071582285199</v>
+      </c>
+      <c r="K34" s="3">
+        <v>20.716535048086971</v>
+      </c>
+      <c r="L34" s="3">
+        <v>24.57314746843609</v>
+      </c>
+      <c r="M34" s="3">
+        <v>39.10399764586321</v>
+      </c>
+      <c r="N34" s="3">
+        <v>37.327001132692523</v>
+      </c>
+      <c r="O34" s="3">
+        <v>53.328147217155852</v>
+      </c>
+      <c r="P34" s="3">
+        <v>39.639880583509573</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>41.137218130572599</v>
+      </c>
+      <c r="R34" s="3">
+        <v>29.408907242847839</v>
+      </c>
+      <c r="S34" s="3">
+        <v>52.67888022700631</v>
+      </c>
+      <c r="T34" s="3">
+        <v>59.651956225549149</v>
+      </c>
+      <c r="U34" s="3">
+        <v>57.829235793506129</v>
+      </c>
+      <c r="V34" s="3">
+        <v>2.4146787620237262</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0.69068433214683023</v>
+      </c>
+      <c r="X34" s="3">
+        <v>1586</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>227</v>
+      </c>
+      <c r="Z34">
+        <v>9.9056096483427609</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B35" t="s">
+        <v>280</v>
+      </c>
+      <c r="C35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D35" s="3">
+        <v>13.475901330887909</v>
+      </c>
+      <c r="E35" s="3">
+        <v>17.654190589248909</v>
+      </c>
+      <c r="F35" s="3">
+        <v>17.276609601341011</v>
+      </c>
+      <c r="G35" s="3">
+        <v>13.772524342971369</v>
+      </c>
+      <c r="H35" s="3">
+        <v>11.22613037075415</v>
+      </c>
+      <c r="I35" s="3">
+        <v>9.6343001215110533</v>
+      </c>
+      <c r="J35" s="3">
+        <v>24.048364434409429</v>
+      </c>
+      <c r="K35" s="3">
+        <v>16.413302415326001</v>
+      </c>
+      <c r="L35" s="3">
+        <v>30.07097538374347</v>
+      </c>
+      <c r="M35" s="3">
+        <v>52.941518995898143</v>
+      </c>
+      <c r="N35" s="3">
+        <v>56.008848160965613</v>
+      </c>
+      <c r="O35" s="3">
+        <v>51.956672990593553</v>
+      </c>
+      <c r="P35" s="3">
+        <v>25.024130079985461</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>61.250276863876167</v>
+      </c>
+      <c r="R35" s="3">
+        <v>34.531760350454732</v>
+      </c>
+      <c r="S35" s="3">
+        <v>73.253230542088104</v>
+      </c>
+      <c r="T35" s="3">
+        <v>70.843653870651508</v>
+      </c>
+      <c r="U35" s="3">
+        <v>47.016452689864607</v>
+      </c>
+      <c r="V35" s="3">
+        <v>5.6908108715477592</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1.619289165911586</v>
+      </c>
+      <c r="X35" s="3">
+        <v>2050</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>280</v>
+      </c>
+      <c r="Z35">
+        <v>5.5389024576874979</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" s="3">
+        <v>12.354937469022341</v>
+      </c>
+      <c r="E36" s="3">
+        <v>12.14955987575056</v>
+      </c>
+      <c r="F36" s="3">
+        <v>22.051834089750059</v>
+      </c>
+      <c r="G36" s="3">
+        <v>13.41537165893658</v>
+      </c>
+      <c r="H36" s="3">
+        <v>9.4924628995709313</v>
+      </c>
+      <c r="I36" s="3">
+        <v>5.0541568459456228</v>
+      </c>
+      <c r="J36" s="3">
+        <v>19.88110288358201</v>
+      </c>
+      <c r="K36" s="3">
+        <v>16.235945202757851</v>
+      </c>
+      <c r="L36" s="3">
+        <v>27.926318714037158</v>
+      </c>
+      <c r="M36" s="3">
+        <v>49.913850226238793</v>
+      </c>
+      <c r="N36" s="3">
+        <v>45.576162169072717</v>
+      </c>
+      <c r="O36" s="3">
+        <v>71.065817394537618</v>
+      </c>
+      <c r="P36" s="3">
+        <v>58.330549146076287</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>67.954471556730667</v>
+      </c>
+      <c r="R36" s="3">
+        <v>30.919558756999891</v>
+      </c>
+      <c r="S36" s="3">
+        <v>62.440353978869638</v>
+      </c>
+      <c r="T36" s="3">
+        <v>53.474131947780421</v>
+      </c>
+      <c r="U36" s="3">
+        <v>62.157584610157421</v>
+      </c>
+      <c r="V36" s="3">
+        <v>2.346294247748999</v>
+      </c>
+      <c r="W36" s="3">
+        <v>2.0798599818053201</v>
+      </c>
+      <c r="X36" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>242</v>
+      </c>
+      <c r="Z36">
+        <v>4.0265412880044504</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B37" t="s">
+        <v>280</v>
+      </c>
+      <c r="C37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D37" s="3">
+        <v>6.6604600247217611</v>
+      </c>
+      <c r="E37" s="3">
+        <v>10.19108280254777</v>
+      </c>
+      <c r="F37" s="3">
+        <v>13.4545454545454</v>
+      </c>
+      <c r="G37" s="3">
+        <v>6.1882049786323012</v>
+      </c>
+      <c r="H37" s="3">
+        <v>3.805792326674506</v>
+      </c>
+      <c r="I37" s="3">
+        <v>2.7472760844821051</v>
+      </c>
+      <c r="J37" s="3">
+        <v>9.7272435817468939</v>
+      </c>
+      <c r="K37" s="3">
+        <v>17.158932932931378</v>
+      </c>
+      <c r="L37" s="3">
+        <v>16.087059667895879</v>
+      </c>
+      <c r="M37" s="3">
+        <v>44.878360639772389</v>
+      </c>
+      <c r="N37" s="3">
+        <v>42.96944809802153</v>
+      </c>
+      <c r="O37" s="3">
+        <v>58.538886794498957</v>
+      </c>
+      <c r="P37" s="3">
+        <v>51.4929029394388</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>54.595886700082673</v>
+      </c>
+      <c r="R37" s="3">
+        <v>61.026923009431819</v>
+      </c>
+      <c r="S37" s="3">
+        <v>68.213127856319005</v>
+      </c>
+      <c r="T37" s="3">
+        <v>85.870450440331879</v>
+      </c>
+      <c r="U37" s="3">
+        <v>83.640496393056935</v>
+      </c>
+      <c r="V37" s="3">
+        <v>2.1886086004552689</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0.79365492756929368</v>
+      </c>
+      <c r="X37" s="3">
+        <v>1556</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z37">
+        <v>8.4946805347907581</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B38" t="s">
+        <v>280</v>
+      </c>
+      <c r="C38" t="s">
+        <v>281</v>
+      </c>
+      <c r="D38" s="3">
+        <v>6.3880968011907528</v>
+      </c>
+      <c r="E38" s="3">
+        <v>4.3946147958035144</v>
+      </c>
+      <c r="F38" s="3">
+        <v>10.37675313960942</v>
+      </c>
+      <c r="G38" s="3">
+        <v>5.9944532488114692</v>
+      </c>
+      <c r="H38" s="3">
+        <v>7.2658710997677787</v>
+      </c>
+      <c r="I38" s="3">
+        <v>2.6606589976590231</v>
+      </c>
+      <c r="J38" s="3">
+        <v>9.5803911938780715</v>
+      </c>
+      <c r="K38" s="3">
+        <v>13.506863182371809</v>
+      </c>
+      <c r="L38" s="3">
+        <v>7.8985071362170212</v>
+      </c>
+      <c r="M38" s="3">
+        <v>54.375247440401523</v>
+      </c>
+      <c r="N38" s="3">
+        <v>46.03874538745405</v>
+      </c>
+      <c r="O38" s="3">
+        <v>41.759987623320633</v>
+      </c>
+      <c r="P38" s="3">
+        <v>33.386719231243099</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>53.859216216933568</v>
+      </c>
+      <c r="R38" s="3">
+        <v>25.793127581531081</v>
+      </c>
+      <c r="S38" s="3">
+        <v>52.378667626263663</v>
+      </c>
+      <c r="T38" s="3">
+        <v>55.582019479583593</v>
+      </c>
+      <c r="U38" s="3">
+        <v>43.356830432979862</v>
+      </c>
+      <c r="V38" s="3">
+        <v>2.8334744892078549</v>
+      </c>
+      <c r="W38" s="3">
+        <v>0.80383676701262785</v>
+      </c>
+      <c r="X38" s="3">
+        <v>2013</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>130</v>
+      </c>
+      <c r="Z38">
+        <v>6.4788040672938054</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B39" t="s">
+        <v>304</v>
+      </c>
+      <c r="C39" t="s">
+        <v>283</v>
+      </c>
+      <c r="D39" s="3">
+        <v>28.25904920773954</v>
+      </c>
+      <c r="E39" s="3">
+        <v>28.508817982290381</v>
+      </c>
+      <c r="F39" s="3">
+        <v>33.463177237553751</v>
+      </c>
+      <c r="G39" s="3">
+        <v>28.7524308276735</v>
+      </c>
+      <c r="H39" s="3">
+        <v>25.611858932482491</v>
+      </c>
+      <c r="I39" s="3">
+        <v>13.365585796906441</v>
+      </c>
+      <c r="J39" s="3">
+        <v>17.932050408816298</v>
+      </c>
+      <c r="K39" s="3">
+        <v>29.79630803114312</v>
+      </c>
+      <c r="L39" s="3">
+        <v>46.334792188678698</v>
+      </c>
+      <c r="M39" s="3">
+        <v>40.253995283871873</v>
+      </c>
+      <c r="N39" s="3">
+        <v>41.454192602448202</v>
+      </c>
+      <c r="O39" s="3">
+        <v>76.327279419460979</v>
+      </c>
+      <c r="P39" s="3">
+        <v>69.110946397987462</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>71.11250936768414</v>
+      </c>
+      <c r="R39" s="3">
+        <v>48.829028551203272</v>
+      </c>
+      <c r="S39" s="3">
+        <v>94.166224851037455</v>
+      </c>
+      <c r="T39" s="3">
+        <v>79.83153727642015</v>
+      </c>
+      <c r="U39" s="3">
+        <v>63.483002396826762</v>
+      </c>
+      <c r="V39" s="3">
+        <v>7.2786295519236184</v>
+      </c>
+      <c r="W39" s="3">
+        <v>1.7865086598870901</v>
+      </c>
+      <c r="X39" s="3">
+        <v>2860</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>840</v>
+      </c>
+      <c r="Z39">
+        <v>12.680122906607689</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="3">
+        <v>21.7673489765352</v>
+      </c>
+      <c r="E40" s="3">
+        <v>21.02425876010782</v>
+      </c>
+      <c r="F40" s="3">
+        <v>24.744376278118612</v>
+      </c>
+      <c r="G40" s="3">
+        <v>27.17622080679406</v>
+      </c>
+      <c r="H40" s="3">
+        <v>18.89168765743073</v>
+      </c>
+      <c r="I40" s="3">
+        <v>12.36363636363636</v>
+      </c>
+      <c r="J40" s="3">
+        <v>31.90214677983025</v>
+      </c>
+      <c r="K40" s="3">
+        <v>11.18322516225661</v>
+      </c>
+      <c r="L40" s="3">
+        <v>49.14400805639476</v>
+      </c>
+      <c r="M40" s="3">
+        <v>41.487768347478777</v>
+      </c>
+      <c r="N40" s="3">
+        <v>45.554035567715459</v>
+      </c>
+      <c r="O40" s="3">
+        <v>69.756662804171498</v>
+      </c>
+      <c r="P40" s="3">
+        <v>46.295123495883473</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>45.331325301204807</v>
+      </c>
+      <c r="R40" s="3">
+        <v>49.124924562462283</v>
+      </c>
+      <c r="S40" s="3">
+        <v>64.159292035398224</v>
+      </c>
+      <c r="T40" s="3">
+        <v>66.393958464443045</v>
+      </c>
+      <c r="U40" s="3">
+        <v>68.125369603784748</v>
+      </c>
+      <c r="V40" s="3">
+        <v>9.0409590409590415</v>
+      </c>
+      <c r="W40" s="3">
+        <v>2.346480279580629</v>
+      </c>
+      <c r="X40" s="3">
+        <v>2003</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>436</v>
+      </c>
+      <c r="Z40">
+        <v>3.7443834248627059</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C41" t="s">
+        <v>281</v>
+      </c>
+      <c r="D41" s="3">
+        <v>23.05709854026864</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19.852539575208759</v>
+      </c>
+      <c r="F41" s="3">
+        <v>31.490435059568419</v>
+      </c>
+      <c r="G41" s="3">
+        <v>26.403480625346941</v>
+      </c>
+      <c r="H41" s="3">
+        <v>24.627357294078859</v>
+      </c>
+      <c r="I41" s="3">
+        <v>9.065518908333031</v>
+      </c>
+      <c r="J41" s="3">
+        <v>28.132339704396699</v>
+      </c>
+      <c r="K41" s="3">
+        <v>16.171395332828052</v>
+      </c>
+      <c r="L41" s="3">
+        <v>36.63885207263305</v>
+      </c>
+      <c r="M41" s="3">
+        <v>51.720413347355652</v>
+      </c>
+      <c r="N41" s="3">
+        <v>48.231955021402939</v>
+      </c>
+      <c r="O41" s="3">
+        <v>69.785658255740131</v>
+      </c>
+      <c r="P41" s="3">
+        <v>58.441418371984469</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>54.523722564249447</v>
+      </c>
+      <c r="R41" s="3">
+        <v>37.703853813485352</v>
+      </c>
+      <c r="S41" s="3">
+        <v>68.959999031215617</v>
+      </c>
+      <c r="T41" s="3">
+        <v>63.31659628953453</v>
+      </c>
+      <c r="U41" s="3">
+        <v>68.423116282173112</v>
+      </c>
+      <c r="V41" s="3">
+        <v>7.6849189141804661</v>
+      </c>
+      <c r="W41" s="3">
+        <v>1.999078901396387</v>
+      </c>
+      <c r="X41" s="3">
+        <v>1735</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>435</v>
+      </c>
+      <c r="Z41">
+        <v>4.0969921984373414</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B42" t="s">
+        <v>308</v>
+      </c>
+      <c r="C42" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="3">
+        <v>19.90714280506436</v>
+      </c>
+      <c r="E42" s="3">
+        <v>19.203135014808922</v>
+      </c>
+      <c r="F42" s="3">
+        <v>22.238113406438949</v>
+      </c>
+      <c r="G42" s="3">
+        <v>21.998379120638599</v>
+      </c>
+      <c r="H42" s="3">
+        <v>11.371833395058641</v>
+      </c>
+      <c r="I42" s="3">
+        <v>23.492326902428388</v>
+      </c>
+      <c r="J42" s="3">
+        <v>32.619247029484207</v>
+      </c>
+      <c r="K42" s="3">
+        <v>21.845680214520549</v>
+      </c>
+      <c r="L42" s="3">
+        <v>63.632389950928449</v>
+      </c>
+      <c r="M42" s="3">
+        <v>12.985389524312721</v>
+      </c>
+      <c r="N42" s="3">
+        <v>12.07584135883433</v>
+      </c>
+      <c r="O42" s="3">
+        <v>65.418441338037411</v>
+      </c>
+      <c r="P42" s="3">
+        <v>51.35303150662233</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>53.374074051718416</v>
+      </c>
+      <c r="R42" s="3">
+        <v>52.384992031441143</v>
+      </c>
+      <c r="S42" s="3">
+        <v>90.989537170438211</v>
+      </c>
+      <c r="T42" s="3">
+        <v>91.711274927597231</v>
+      </c>
+      <c r="U42" s="3">
+        <v>62.494663772567009</v>
+      </c>
+      <c r="V42" s="3">
+        <v>16.63688615586663</v>
+      </c>
+      <c r="W42" s="3">
+        <v>1.341821762696326</v>
+      </c>
+      <c r="X42" s="3">
+        <v>1854</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>370</v>
+      </c>
+      <c r="Z42">
+        <v>12.09665722556913</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B43" t="s">
+        <v>304</v>
+      </c>
+      <c r="C43" t="s">
+        <v>283</v>
+      </c>
+      <c r="D43" s="3">
+        <v>41.942935277535028</v>
+      </c>
+      <c r="E43" s="3">
+        <v>37.830637114639117</v>
+      </c>
+      <c r="F43" s="3">
+        <v>44.589579048597557</v>
+      </c>
+      <c r="G43" s="3">
+        <v>48.328853104305288</v>
+      </c>
+      <c r="H43" s="3">
+        <v>44.727114607033897</v>
+      </c>
+      <c r="I43" s="3">
+        <v>28.758227947806251</v>
+      </c>
+      <c r="J43" s="3">
+        <v>62.115572092183207</v>
+      </c>
+      <c r="K43" s="3">
+        <v>47.165219450622182</v>
+      </c>
+      <c r="L43" s="3">
+        <v>59.311606780190083</v>
+      </c>
+      <c r="M43" s="3">
+        <v>37.496180663093952</v>
+      </c>
+      <c r="N43" s="3">
+        <v>36.714320438686258</v>
+      </c>
+      <c r="O43" s="3">
+        <v>88.683806880924678</v>
+      </c>
+      <c r="P43" s="3">
+        <v>74.359190789431906</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>82.665501566824247</v>
+      </c>
+      <c r="R43" s="3">
+        <v>66.557688313880575</v>
+      </c>
+      <c r="S43" s="3">
+        <v>86.243969734851134</v>
+      </c>
+      <c r="T43" s="3">
+        <v>89.841227584059325</v>
+      </c>
+      <c r="U43" s="3">
+        <v>89.605626775087359</v>
+      </c>
+      <c r="V43" s="3">
+        <v>10.06051120256164</v>
+      </c>
+      <c r="W43" s="3">
+        <v>4.6667049318256364</v>
+      </c>
+      <c r="X43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>838</v>
+      </c>
+      <c r="Z43">
+        <v>3.843371001082863</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B44" t="s">
+        <v>286</v>
+      </c>
+      <c r="C44" t="s">
+        <v>281</v>
+      </c>
+      <c r="D44" s="3">
+        <v>19.61742389021731</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15.84014134161818</v>
+      </c>
+      <c r="F44" s="3">
+        <v>20.663634957196219</v>
+      </c>
+      <c r="G44" s="3">
+        <v>21.280640536692619</v>
+      </c>
+      <c r="H44" s="3">
+        <v>18.262268437443151</v>
+      </c>
+      <c r="I44" s="3">
+        <v>20.161375660606971</v>
+      </c>
+      <c r="J44" s="3">
+        <v>23.40733664987534</v>
+      </c>
+      <c r="K44" s="3">
+        <v>14.667890078038139</v>
+      </c>
+      <c r="L44" s="3">
+        <v>23.0136789069652</v>
+      </c>
+      <c r="M44" s="3">
+        <v>53.023636051009653</v>
+      </c>
+      <c r="N44" s="3">
+        <v>53.612966585627433</v>
+      </c>
+      <c r="O44" s="3">
+        <v>90.507154355484261</v>
+      </c>
+      <c r="P44" s="3">
+        <v>95.378167974667065</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>57.945214291453482</v>
+      </c>
+      <c r="R44" s="3">
+        <v>93.540085340926296</v>
+      </c>
+      <c r="S44" s="3">
+        <v>96.554621702471437</v>
+      </c>
+      <c r="T44" s="3">
+        <v>96.327957861945606</v>
+      </c>
+      <c r="U44" s="3">
+        <v>95.490363309714837</v>
+      </c>
+      <c r="V44" s="3">
+        <v>5.6948752754460763</v>
+      </c>
+      <c r="W44" s="3">
+        <v>2.9114928718351041</v>
+      </c>
+      <c r="X44" s="3">
+        <v>4032</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>792</v>
+      </c>
+      <c r="Z44">
+        <v>5.3299932850645151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B45" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" t="s">
+        <v>281</v>
+      </c>
+      <c r="D45" s="3">
+        <v>12.69787906758012</v>
+      </c>
+      <c r="E45" s="3">
+        <v>12.61101243339253</v>
+      </c>
+      <c r="F45" s="3">
+        <v>17.24137931034484</v>
+      </c>
+      <c r="G45" s="3">
+        <v>12.606837606837701</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5.3571428571428754</v>
+      </c>
+      <c r="I45" s="3">
+        <v>5.1470588235294006</v>
+      </c>
+      <c r="J45" s="3">
+        <v>31.82204078773875</v>
+      </c>
+      <c r="K45" s="3">
+        <v>16.153305467798209</v>
+      </c>
+      <c r="L45" s="3">
+        <v>55.148752467038378</v>
+      </c>
+      <c r="M45" s="3">
+        <v>23.076114934075601</v>
+      </c>
+      <c r="N45" s="3">
+        <v>24.631409891137078</v>
+      </c>
+      <c r="O45" s="3">
+        <v>59.170407021809737</v>
+      </c>
+      <c r="P45" s="3">
+        <v>67.704603944880972</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>69.411930807722158</v>
+      </c>
+      <c r="R45" s="3">
+        <v>44.513211838132968</v>
+      </c>
+      <c r="S45" s="3">
+        <v>77.902112354647798</v>
+      </c>
+      <c r="T45" s="3">
+        <v>75.651579832286387</v>
+      </c>
+      <c r="U45" s="3">
+        <v>71.25306007988344</v>
+      </c>
+      <c r="V45" s="3">
+        <v>10.14837575230216</v>
+      </c>
+      <c r="W45" s="3">
+        <v>3.5557323207688021</v>
+      </c>
+      <c r="X45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>254</v>
+      </c>
+      <c r="Z45">
+        <v>2.8387826213113598</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" t="s">
+        <v>286</v>
+      </c>
+      <c r="C46" t="s">
+        <v>281</v>
+      </c>
+      <c r="D46" s="3">
+        <v>16.508313025412061</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17.39214097349382</v>
+      </c>
+      <c r="F46" s="3">
+        <v>15.696764163486259</v>
+      </c>
+      <c r="G46" s="3">
+        <v>18.837130640587581</v>
+      </c>
+      <c r="H46" s="3">
+        <v>14.45377820136949</v>
+      </c>
+      <c r="I46" s="3">
+        <v>12.18318081914426</v>
+      </c>
+      <c r="J46" s="3">
+        <v>29.730629633404419</v>
+      </c>
+      <c r="K46" s="3">
+        <v>22.595153153221379</v>
+      </c>
+      <c r="L46" s="3">
+        <v>42.641724687761752</v>
+      </c>
+      <c r="M46" s="3">
+        <v>47.227900561997117</v>
+      </c>
+      <c r="N46" s="3">
+        <v>49.717649591638882</v>
+      </c>
+      <c r="O46" s="3">
+        <v>65.119235582729544</v>
+      </c>
+      <c r="P46" s="3">
+        <v>73.468639805778352</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>54.561445356696261</v>
+      </c>
+      <c r="R46" s="3">
+        <v>74.417745152152747</v>
+      </c>
+      <c r="S46" s="3">
+        <v>74.316095110913977</v>
+      </c>
+      <c r="T46" s="3">
+        <v>79.142440113542506</v>
+      </c>
+      <c r="U46" s="3">
+        <v>81.596310889414411</v>
+      </c>
+      <c r="V46" s="3">
+        <v>6.7311339099561192</v>
+      </c>
+      <c r="W46" s="3">
+        <v>3.5259419459772698</v>
+      </c>
+      <c r="X46" s="3">
+        <v>2006</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>331</v>
+      </c>
+      <c r="Z46">
+        <v>6.4025249060972138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D47" s="3">
+        <v>9.5507812165545012</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4.8381640127145804</v>
+      </c>
+      <c r="F47" s="3">
+        <v>12.67226564231539</v>
+      </c>
+      <c r="G47" s="3">
+        <v>9.5843734660077562</v>
+      </c>
+      <c r="H47" s="3">
+        <v>10.02123314423288</v>
+      </c>
+      <c r="I47" s="3">
+        <v>9.4874634205927322</v>
+      </c>
+      <c r="J47" s="3">
+        <v>13.309286691066911</v>
+      </c>
+      <c r="K47" s="3">
+        <v>13.33171824586668</v>
+      </c>
+      <c r="L47" s="3">
+        <v>19.856367963405379</v>
+      </c>
+      <c r="M47" s="3">
+        <v>53.797021663411861</v>
+      </c>
+      <c r="N47" s="3">
+        <v>46.588019306815923</v>
+      </c>
+      <c r="O47" s="3">
+        <v>37.539920964293962</v>
+      </c>
+      <c r="P47" s="3">
+        <v>45.833873863367963</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>63.475820280083148</v>
+      </c>
+      <c r="R47" s="3">
+        <v>13.717024860696471</v>
+      </c>
+      <c r="S47" s="3">
+        <v>63.32598256673905</v>
+      </c>
+      <c r="T47" s="3">
+        <v>82.648922141104237</v>
+      </c>
+      <c r="U47" s="3">
+        <v>53.277967566082992</v>
+      </c>
+      <c r="V47" s="3">
+        <v>3.329936073750305</v>
+      </c>
+      <c r="W47" s="3">
+        <v>1.1927764267380749</v>
+      </c>
+      <c r="X47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>191</v>
+      </c>
+      <c r="Z47">
+        <v>3.3380500448666242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B48" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D48" s="3">
+        <v>15.8674524281586</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12.29238363453843</v>
+      </c>
+      <c r="F48" s="3">
+        <v>17.196400850755019</v>
+      </c>
+      <c r="G48" s="3">
+        <v>15.952348897047649</v>
+      </c>
+      <c r="H48" s="3">
+        <v>15.391038223663671</v>
+      </c>
+      <c r="I48" s="3">
+        <v>16.17505582508829</v>
+      </c>
+      <c r="J48" s="3">
+        <v>26.966582789547662</v>
+      </c>
+      <c r="K48" s="3">
+        <v>16.040270365486599</v>
+      </c>
+      <c r="L48" s="3">
+        <v>54.746641224213462</v>
+      </c>
+      <c r="M48" s="3">
+        <v>39.517090686381067</v>
+      </c>
+      <c r="N48" s="3">
+        <v>38.175206496028778</v>
+      </c>
+      <c r="O48" s="3">
+        <v>70.905365438028269</v>
+      </c>
+      <c r="P48" s="3">
+        <v>73.792320787842797</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>55.904826352628582</v>
+      </c>
+      <c r="R48" s="3">
+        <v>64.187349886576499</v>
+      </c>
+      <c r="S48" s="3">
+        <v>79.474923612688642</v>
+      </c>
+      <c r="T48" s="3">
+        <v>87.68930448031297</v>
+      </c>
+      <c r="U48" s="3">
+        <v>80.754876403205273</v>
+      </c>
+      <c r="V48" s="3">
+        <v>8.7569573072949947</v>
+      </c>
+      <c r="W48" s="3">
+        <v>2.7486672565932109</v>
+      </c>
+      <c r="X48" s="3">
+        <v>3012</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>511</v>
+      </c>
+      <c r="Z48">
+        <v>6.0707767612392303</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>